--- a/output/pdf_financials_xlsx/AREE.xlsx
+++ b/output/pdf_financials_xlsx/AREE.xlsx
@@ -2203,16 +2203,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.101939</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.286841</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.412562</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.326518</v>
       </c>
     </row>
     <row r="93">
@@ -3516,7 +3516,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -3806,7 +3810,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>0.101939</v>
       </c>

--- a/output/pdf_financials_xlsx/AREE.xlsx
+++ b/output/pdf_financials_xlsx/AREE.xlsx
@@ -645,7 +645,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.050205</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>-1.07094</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.113926</v>
+        <v>-1.164131</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.6257470000000001</v>
@@ -992,7 +992,7 @@
         <v>-1.07094</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.113926</v>
+        <v>-1.164131</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.6257470000000001</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">

--- a/output/pdf_financials_xlsx/AREE.xlsx
+++ b/output/pdf_financials_xlsx/AREE.xlsx
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.024055</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.020626</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0</v>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
